--- a/US_AI_ML_Layer_Stack.xlsx
+++ b/US_AI_ML_Layer_Stack.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,6 +99,18 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00BF9000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="8.5"/>
@@ -110,7 +122,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +159,31 @@
         <fgColor rgb="00BF9000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -174,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,10 +268,43 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1523,25 +1593,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>US AI/ML UNICORNS BY STACK LAYER — 170 companies (as of 2026-06-30)</t>
+          <t>US AI/ML UNICORNS BY STACK LAYER — 170 companies (as of 2026-06-30) — AIBQ code + composite + revenue for ALL</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1629,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>PitchBook sector</t>
+          <t>AIBQ code</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -1583,15 +1654,20 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t>AIBQ code</t>
+          <t>AIBQ composite</t>
         </is>
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
-          <t>AIBQ composite</t>
+          <t>Tier</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>Score type</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
@@ -1615,9 +1691,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -1632,15 +1708,20 @@
       <c r="G5" s="17" t="n">
         <v>47000</v>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>AI-INFRA</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="n">
+      <c r="H5" s="24" t="n">
         <v>7.22</v>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -1657,9 +1738,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -1674,15 +1755,20 @@
       <c r="G6" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>AI-INFRA</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="n">
+      <c r="H6" s="27" t="n">
         <v>6.3</v>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -1699,9 +1785,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
@@ -1714,9 +1800,20 @@
       <c r="G7" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="17" t="inlineStr"/>
+      <c r="H7" s="27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -1733,9 +1830,9 @@
           <t>Foundation model (stealth)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
@@ -1746,9 +1843,20 @@
         <v>16.2</v>
       </c>
       <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="17" t="inlineStr"/>
+      <c r="H8" s="27" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -1765,9 +1873,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
@@ -1778,9 +1886,20 @@
         <v>3</v>
       </c>
       <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="17" t="inlineStr"/>
+      <c r="H9" s="27" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -1797,9 +1916,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
@@ -1812,9 +1931,20 @@
       <c r="G10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="17" t="inlineStr"/>
+      <c r="H10" s="27" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -1831,9 +1961,9 @@
           <t>Frontier LLM lab</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
@@ -1844,9 +1974,20 @@
         <v>2</v>
       </c>
       <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="inlineStr"/>
-      <c r="I11" s="17" t="inlineStr"/>
+      <c r="H11" s="27" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -1863,9 +2004,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D12" s="17" t="n">
@@ -1876,9 +2017,20 @@
         <v>0.55</v>
       </c>
       <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="17" t="inlineStr"/>
+      <c r="H12" s="27" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -1895,9 +2047,9 @@
           <t>World / spatial models</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
@@ -1908,9 +2060,20 @@
         <v>1.29</v>
       </c>
       <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="inlineStr"/>
-      <c r="I13" s="17" t="inlineStr"/>
+      <c r="H13" s="27" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -1927,9 +2090,9 @@
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D14" s="17" t="n">
@@ -1940,9 +2103,20 @@
         <v>1.56</v>
       </c>
       <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="inlineStr"/>
-      <c r="I14" s="17" t="inlineStr"/>
+      <c r="H14" s="27" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I14" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -1959,9 +2133,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
@@ -1974,9 +2148,20 @@
       <c r="G15" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="17" t="inlineStr"/>
+      <c r="H15" s="27" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -1993,9 +2178,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D16" s="17" t="n">
@@ -2008,9 +2193,20 @@
       <c r="G16" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H16" s="17" t="inlineStr"/>
-      <c r="I16" s="17" t="inlineStr"/>
+      <c r="H16" s="27" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2027,9 +2223,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
@@ -2040,9 +2236,20 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="inlineStr"/>
-      <c r="I17" s="17" t="inlineStr"/>
+      <c r="H17" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2059,9 +2266,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D18" s="17" t="n">
@@ -2072,9 +2279,20 @@
         <v>0.54</v>
       </c>
       <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="inlineStr"/>
-      <c r="I18" s="17" t="inlineStr"/>
+      <c r="H18" s="27" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2091,9 +2309,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D19" s="17" t="n">
@@ -2104,9 +2322,20 @@
         <v>0.26</v>
       </c>
       <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="inlineStr"/>
-      <c r="I19" s="17" t="inlineStr"/>
+      <c r="H19" s="27" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2123,9 +2352,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D20" s="17" t="n">
@@ -2138,9 +2367,20 @@
       <c r="G20" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="17" t="inlineStr"/>
-      <c r="I20" s="17" t="inlineStr"/>
+      <c r="H20" s="30" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I20" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2157,9 +2397,9 @@
           <t>Foundation model developer</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D21" s="17" t="n">
@@ -2172,9 +2412,20 @@
       <c r="G21" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="17" t="inlineStr"/>
-      <c r="I21" s="17" t="inlineStr"/>
+      <c r="H21" s="27" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I21" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2191,9 +2442,9 @@
           <t>Foundation model / agents</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D22" s="17" t="n">
@@ -2206,9 +2457,20 @@
       <c r="G22" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="17" t="inlineStr"/>
-      <c r="I22" s="17" t="inlineStr"/>
+      <c r="H22" s="30" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2225,9 +2487,9 @@
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D23" s="17" t="n">
@@ -2238,9 +2500,20 @@
         <v>0.17</v>
       </c>
       <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="inlineStr"/>
-      <c r="I23" s="17" t="inlineStr"/>
+      <c r="H23" s="30" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2264,9 +2537,9 @@
           <t>Data + AI platform</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D25" s="17" t="n">
@@ -2281,15 +2554,20 @@
       <c r="G25" s="17" t="n">
         <v>5400</v>
       </c>
-      <c r="H25" s="23" t="inlineStr">
-        <is>
-          <t>AI-PLAT</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="n">
+      <c r="H25" s="32" t="n">
         <v>8.19</v>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -2306,9 +2584,9 @@
           <t>Training data / labeling</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D26" s="17" t="n">
@@ -2321,9 +2599,20 @@
       <c r="G26" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="H26" s="17" t="inlineStr"/>
-      <c r="I26" s="17" t="inlineStr"/>
+      <c r="H26" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2340,9 +2629,9 @@
           <t>AI data platform / storage</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D27" s="17" t="n">
@@ -2353,9 +2642,20 @@
         <v>1.4</v>
       </c>
       <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="inlineStr"/>
-      <c r="I27" s="17" t="inlineStr"/>
+      <c r="H27" s="27" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="I27" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
@@ -2372,9 +2672,9 @@
           <t>GPU cloud / neocloud</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D28" s="17" t="n">
@@ -2387,9 +2687,20 @@
       <c r="G28" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="H28" s="17" t="inlineStr"/>
-      <c r="I28" s="17" t="inlineStr"/>
+      <c r="H28" s="27" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="I28" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2406,9 +2717,9 @@
           <t>Training data / talent</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D29" s="17" t="n">
@@ -2421,9 +2732,20 @@
       <c r="G29" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="H29" s="17" t="inlineStr"/>
-      <c r="I29" s="17" t="inlineStr"/>
+      <c r="H29" s="27" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="I29" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2440,9 +2762,9 @@
           <t>GPU cloud / neocloud</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D30" s="17" t="n">
@@ -2455,9 +2777,20 @@
       <c r="G30" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="H30" s="17" t="inlineStr"/>
-      <c r="I30" s="17" t="inlineStr"/>
+      <c r="H30" s="27" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="I30" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2474,9 +2807,9 @@
           <t>GPU cloud / neocloud</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D31" s="17" t="n">
@@ -2489,9 +2822,20 @@
       <c r="G31" s="17" t="n">
         <v>520</v>
       </c>
-      <c r="H31" s="17" t="inlineStr"/>
-      <c r="I31" s="17" t="inlineStr"/>
+      <c r="H31" s="27" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I31" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2508,9 +2852,9 @@
           <t>AI accelerator (silicon)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D32" s="17" t="n">
@@ -2523,9 +2867,20 @@
       <c r="G32" s="17" t="n">
         <v>164</v>
       </c>
-      <c r="H32" s="17" t="inlineStr"/>
-      <c r="I32" s="17" t="inlineStr"/>
+      <c r="H32" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I32" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2542,9 +2897,9 @@
           <t>AI accelerator (silicon)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D33" s="17" t="n">
@@ -2555,9 +2910,20 @@
         <v>0.74</v>
       </c>
       <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="inlineStr"/>
-      <c r="I33" s="17" t="inlineStr"/>
+      <c r="H33" s="27" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I33" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2574,9 +2940,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D34" s="17" t="n">
@@ -2589,9 +2955,20 @@
       <c r="G34" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="H34" s="17" t="inlineStr"/>
-      <c r="I34" s="17" t="inlineStr"/>
+      <c r="H34" s="27" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I34" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -2608,9 +2985,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D35" s="17" t="n">
@@ -2621,9 +2998,20 @@
         <v>0.11</v>
       </c>
       <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="inlineStr"/>
-      <c r="I35" s="17" t="inlineStr"/>
+      <c r="H35" s="27" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="I35" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J35" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -2640,9 +3028,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D36" s="17" t="n">
@@ -2653,9 +3041,20 @@
         <v>0.82</v>
       </c>
       <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="inlineStr"/>
-      <c r="I36" s="17" t="inlineStr"/>
+      <c r="H36" s="27" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="I36" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2672,9 +3071,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D37" s="17" t="n">
@@ -2685,9 +3084,20 @@
         <v>0.61</v>
       </c>
       <c r="G37" s="17" t="n"/>
-      <c r="H37" s="17" t="inlineStr"/>
-      <c r="I37" s="17" t="inlineStr"/>
+      <c r="H37" s="27" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I37" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2704,9 +3114,9 @@
           <t>AI data / MLOps</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D38" s="17" t="n">
@@ -2717,9 +3127,20 @@
         <v>0.37</v>
       </c>
       <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="inlineStr"/>
-      <c r="I38" s="17" t="inlineStr"/>
+      <c r="H38" s="27" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="I38" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2736,9 +3157,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D39" s="17" t="n">
@@ -2749,9 +3170,20 @@
         <v>0.34</v>
       </c>
       <c r="G39" s="17" t="n"/>
-      <c r="H39" s="17" t="inlineStr"/>
-      <c r="I39" s="17" t="inlineStr"/>
+      <c r="H39" s="27" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="I39" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2768,9 +3200,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D40" s="17" t="n">
@@ -2781,9 +3213,20 @@
         <v>0.87</v>
       </c>
       <c r="G40" s="17" t="n"/>
-      <c r="H40" s="17" t="inlineStr"/>
-      <c r="I40" s="17" t="inlineStr"/>
+      <c r="H40" s="27" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I40" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2800,9 +3243,9 @@
           <t>AI data / MLOps</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D41" s="17" t="n">
@@ -2815,9 +3258,20 @@
       <c r="G41" s="17" t="n">
         <v>350</v>
       </c>
-      <c r="H41" s="17" t="inlineStr"/>
-      <c r="I41" s="17" t="inlineStr"/>
+      <c r="H41" s="27" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="I41" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2834,9 +3288,9 @@
           <t>AI data / MLOps</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D42" s="17" t="n">
@@ -2847,9 +3301,20 @@
         <v>0.43</v>
       </c>
       <c r="G42" s="17" t="n"/>
-      <c r="H42" s="17" t="inlineStr"/>
-      <c r="I42" s="17" t="inlineStr"/>
+      <c r="H42" s="27" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I42" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2866,9 +3331,9 @@
           <t>AI accelerator (silicon)</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D43" s="17" t="n">
@@ -2879,9 +3344,20 @@
         <v>1.83</v>
       </c>
       <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="inlineStr"/>
-      <c r="I43" s="17" t="inlineStr"/>
+      <c r="H43" s="27" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I43" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2898,9 +3374,9 @@
           <t>Training data / talent</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D44" s="17" t="n">
@@ -2913,9 +3389,20 @@
       <c r="G44" s="17" t="n">
         <v>167</v>
       </c>
-      <c r="H44" s="17" t="inlineStr"/>
-      <c r="I44" s="17" t="inlineStr"/>
+      <c r="H44" s="27" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I44" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J44" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K44" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2932,9 +3419,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D45" s="17" t="n">
@@ -2945,9 +3432,20 @@
         <v>0.35</v>
       </c>
       <c r="G45" s="17" t="n"/>
-      <c r="H45" s="17" t="inlineStr"/>
-      <c r="I45" s="17" t="inlineStr"/>
+      <c r="H45" s="27" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I45" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K45" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2964,9 +3462,9 @@
           <t>AI accelerator (silicon)</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D46" s="17" t="n">
@@ -2977,9 +3475,20 @@
         <v>0.45</v>
       </c>
       <c r="G46" s="17" t="n"/>
-      <c r="H46" s="17" t="inlineStr"/>
-      <c r="I46" s="17" t="inlineStr"/>
+      <c r="H46" s="27" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I46" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J46" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -2996,9 +3505,9 @@
           <t>AI data / MLOps</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D47" s="17" t="n">
@@ -3011,9 +3520,20 @@
       <c r="G47" s="17" t="n">
         <v>133</v>
       </c>
-      <c r="H47" s="17" t="inlineStr"/>
-      <c r="I47" s="17" t="inlineStr"/>
+      <c r="H47" s="27" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I47" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J47" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K47" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3030,9 +3550,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D48" s="17" t="n">
@@ -3045,9 +3565,20 @@
       <c r="G48" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H48" s="17" t="inlineStr"/>
-      <c r="I48" s="17" t="inlineStr"/>
+      <c r="H48" s="27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I48" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J48" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3064,9 +3595,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D49" s="17" t="n">
@@ -3077,9 +3608,20 @@
         <v>0.3</v>
       </c>
       <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="inlineStr"/>
-      <c r="I49" s="17" t="inlineStr"/>
+      <c r="H49" s="30" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I49" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J49" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3096,9 +3638,9 @@
           <t>Training data / tooling</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>AI-PLAT</t>
         </is>
       </c>
       <c r="D50" s="17" t="n">
@@ -3111,9 +3653,20 @@
       <c r="G50" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="H50" s="17" t="inlineStr"/>
-      <c r="I50" s="17" t="inlineStr"/>
+      <c r="H50" s="27" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="I50" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3130,9 +3683,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D51" s="17" t="n">
@@ -3145,9 +3698,20 @@
       <c r="G51" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H51" s="17" t="inlineStr"/>
-      <c r="I51" s="17" t="inlineStr"/>
+      <c r="H51" s="27" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I51" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3164,9 +3728,9 @@
           <t>AI compute / silicon</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D52" s="17" t="n">
@@ -3177,9 +3741,20 @@
         <v>0.34</v>
       </c>
       <c r="G52" s="17" t="n"/>
-      <c r="H52" s="17" t="inlineStr"/>
-      <c r="I52" s="17" t="inlineStr"/>
+      <c r="H52" s="30" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I52" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3196,9 +3771,9 @@
           <t>AI accelerator (silicon)</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>AI-ACCEL</t>
         </is>
       </c>
       <c r="D53" s="17" t="n">
@@ -3209,9 +3784,20 @@
         <v>0.31</v>
       </c>
       <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="inlineStr"/>
-      <c r="I53" s="17" t="inlineStr"/>
+      <c r="H53" s="30" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="I53" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K53" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3228,9 +3814,9 @@
           <t>GPU cloud / neocloud</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>AI-INFRA</t>
         </is>
       </c>
       <c r="D54" s="17" t="n">
@@ -3243,9 +3829,20 @@
       <c r="G54" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="17" t="inlineStr"/>
-      <c r="I54" s="17" t="inlineStr"/>
+      <c r="H54" s="30" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I54" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3269,9 +3866,9 @@
           <t>Physical AI — autonomous driving</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>Consumer Products and Services (B2C)</t>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D56" s="17" t="n">
@@ -3284,9 +3881,20 @@
       <c r="G56" s="17" t="n">
         <v>350</v>
       </c>
-      <c r="H56" s="17" t="inlineStr"/>
-      <c r="I56" s="17" t="inlineStr"/>
+      <c r="H56" s="27" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="I56" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3303,9 +3911,9 @@
           <t>Defense AI / autonomy</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>PBQ (DEFENSE)</t>
         </is>
       </c>
       <c r="D57" s="17" t="n">
@@ -3320,9 +3928,20 @@
       <c r="G57" s="17" t="n">
         <v>4300</v>
       </c>
-      <c r="H57" s="17" t="inlineStr"/>
-      <c r="I57" s="17" t="inlineStr"/>
-      <c r="J57" s="17" t="inlineStr">
+      <c r="H57" s="24" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3339,9 +3958,9 @@
           <t>Coding / dev tools</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D58" s="17" t="n">
@@ -3356,15 +3975,20 @@
       <c r="G58" s="17" t="n">
         <v>6000</v>
       </c>
-      <c r="H58" s="23" t="inlineStr">
-        <is>
-          <t>AI-APP</t>
-        </is>
-      </c>
-      <c r="I58" s="17" t="n">
+      <c r="H58" s="27" t="n">
         <v>6.05</v>
       </c>
-      <c r="J58" s="17" t="inlineStr">
+      <c r="I58" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K58" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3381,9 +4005,9 @@
           <t>Physical AI — humanoid robotics</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D59" s="17" t="n">
@@ -3398,15 +4022,20 @@
       <c r="G59" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t>AI-AUTO</t>
-        </is>
-      </c>
-      <c r="I59" s="17" t="n">
+      <c r="H59" s="30" t="n">
         <v>3.75</v>
       </c>
-      <c r="J59" s="17" t="inlineStr">
+      <c r="I59" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
+      <c r="J59" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K59" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3423,9 +4052,9 @@
           <t>Physical AI — autonomous driving</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D60" s="17" t="n">
@@ -3438,9 +4067,20 @@
       <c r="G60" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="17" t="inlineStr"/>
-      <c r="I60" s="17" t="inlineStr"/>
+      <c r="H60" s="27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I60" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3457,9 +4097,9 @@
           <t>Coding / autonomous agents</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D61" s="17" t="n">
@@ -3472,9 +4112,20 @@
       <c r="G61" s="17" t="n">
         <v>492</v>
       </c>
-      <c r="H61" s="17" t="inlineStr"/>
-      <c r="I61" s="17" t="inlineStr"/>
+      <c r="H61" s="27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I61" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K61" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3491,9 +4142,9 @@
           <t>AI-native fintech / markets</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D62" s="17" t="n">
@@ -3506,9 +4157,20 @@
       <c r="G62" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="H62" s="17" t="inlineStr"/>
-      <c r="I62" s="17" t="inlineStr"/>
+      <c r="H62" s="27" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="I62" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J62" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3525,9 +4187,9 @@
           <t>Search / knowledge</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D63" s="17" t="n">
@@ -3542,15 +4204,20 @@
       <c r="G63" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t>AI-APP</t>
-        </is>
-      </c>
-      <c r="I63" s="17" t="n">
+      <c r="H63" s="27" t="n">
         <v>5.12</v>
       </c>
-      <c r="J63" s="17" t="inlineStr">
+      <c r="I63" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K63" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3567,9 +4234,9 @@
           <t>Customer-experience agents</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D64" s="17" t="n">
@@ -3582,9 +4249,20 @@
       <c r="G64" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="H64" s="17" t="inlineStr"/>
-      <c r="I64" s="17" t="inlineStr"/>
+      <c r="H64" s="27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I64" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3601,9 +4279,9 @@
           <t>Physical AI — autonomy/AV</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D65" s="17" t="n">
@@ -3618,15 +4296,20 @@
       <c r="G65" s="17" t="n">
         <v>800</v>
       </c>
-      <c r="H65" s="23" t="inlineStr">
-        <is>
-          <t>AI-AUTO</t>
-        </is>
-      </c>
-      <c r="I65" s="17" t="n">
+      <c r="H65" s="24" t="n">
         <v>6.91</v>
       </c>
-      <c r="J65" s="17" t="inlineStr">
+      <c r="I65" s="25" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="K65" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3643,9 +4326,9 @@
           <t>Physical AI — robotics</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D66" s="17" t="n">
@@ -3658,9 +4341,20 @@
       <c r="G66" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H66" s="17" t="inlineStr"/>
-      <c r="I66" s="17" t="inlineStr"/>
+      <c r="H66" s="30" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="I66" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3677,9 +4371,9 @@
           <t>Coding / dev tools</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D67" s="17" t="n">
@@ -3692,9 +4386,20 @@
       <c r="G67" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="H67" s="17" t="inlineStr"/>
-      <c r="I67" s="17" t="inlineStr"/>
+      <c r="H67" s="27" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I67" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K67" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -3711,9 +4416,9 @@
           <t>Defense AI / autonomy</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D68" s="17" t="n">
@@ -3726,9 +4431,20 @@
       <c r="G68" s="17" t="n">
         <v>540</v>
       </c>
-      <c r="H68" s="17" t="inlineStr"/>
-      <c r="I68" s="17" t="inlineStr"/>
+      <c r="H68" s="27" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="I68" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J68" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3745,9 +4461,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D69" s="17" t="n">
@@ -3760,9 +4476,20 @@
       <c r="G69" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H69" s="17" t="inlineStr"/>
-      <c r="I69" s="17" t="inlineStr"/>
+      <c r="H69" s="27" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I69" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J69" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K69" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3779,9 +4506,9 @@
           <t>Vertical AI — legal</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D70" s="17" t="n">
@@ -3794,9 +4521,20 @@
       <c r="G70" s="17" t="n">
         <v>190</v>
       </c>
-      <c r="H70" s="17" t="inlineStr"/>
-      <c r="I70" s="17" t="inlineStr"/>
+      <c r="H70" s="27" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="I70" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J70" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K70" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3813,9 +4551,9 @@
           <t>Physical AI — robotics</t>
         </is>
       </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D71" s="17" t="n">
@@ -3826,9 +4564,20 @@
         <v>1.07</v>
       </c>
       <c r="G71" s="17" t="n"/>
-      <c r="H71" s="17" t="inlineStr"/>
-      <c r="I71" s="17" t="inlineStr"/>
+      <c r="H71" s="27" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="I71" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J71" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K71" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3845,9 +4594,9 @@
           <t>Creative / voice AI</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D72" s="17" t="n">
@@ -3860,9 +4609,20 @@
       <c r="G72" s="17" t="n">
         <v>400</v>
       </c>
-      <c r="H72" s="17" t="inlineStr"/>
-      <c r="I72" s="17" t="inlineStr"/>
+      <c r="H72" s="27" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I72" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J72" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K72" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3879,9 +4639,9 @@
           <t>Coding / dev tools</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D73" s="17" t="n">
@@ -3894,9 +4654,20 @@
       <c r="G73" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="H73" s="17" t="inlineStr"/>
-      <c r="I73" s="17" t="inlineStr"/>
+      <c r="H73" s="24" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="I73" s="25" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="J73" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K73" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -3913,9 +4684,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D74" s="17" t="n">
@@ -3928,9 +4699,20 @@
       <c r="G74" s="17" t="n">
         <v>377</v>
       </c>
-      <c r="H74" s="17" t="inlineStr"/>
-      <c r="I74" s="17" t="inlineStr"/>
+      <c r="H74" s="27" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="I74" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3947,9 +4729,9 @@
           <t>Enterprise search / knowledge</t>
         </is>
       </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D75" s="17" t="n">
@@ -3962,9 +4744,20 @@
       <c r="G75" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="H75" s="17" t="inlineStr"/>
-      <c r="I75" s="17" t="inlineStr"/>
+      <c r="H75" s="27" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="I75" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J75" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K75" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -3981,9 +4774,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D76" s="17" t="n">
@@ -3996,9 +4789,20 @@
       <c r="G76" s="17" t="n">
         <v>176</v>
       </c>
-      <c r="H76" s="17" t="inlineStr"/>
-      <c r="I76" s="17" t="inlineStr"/>
+      <c r="H76" s="27" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="I76" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J76" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4015,9 +4819,9 @@
           <t>Physical AI — autonomous driving</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>Consumer Products and Services (B2C)</t>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D77" s="17" t="n">
@@ -4028,9 +4832,20 @@
         <v>2.33</v>
       </c>
       <c r="G77" s="17" t="n"/>
-      <c r="H77" s="17" t="inlineStr"/>
-      <c r="I77" s="17" t="inlineStr"/>
+      <c r="H77" s="27" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="I77" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K77" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4047,9 +4862,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D78" s="17" t="n">
@@ -4060,9 +4875,20 @@
         <v>0.76</v>
       </c>
       <c r="G78" s="17" t="n"/>
-      <c r="H78" s="17" t="inlineStr"/>
-      <c r="I78" s="17" t="inlineStr"/>
+      <c r="H78" s="27" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="I78" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4079,9 +4905,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D79" s="17" t="n">
@@ -4092,9 +4918,20 @@
         <v>0.95</v>
       </c>
       <c r="G79" s="17" t="n"/>
-      <c r="H79" s="17" t="inlineStr"/>
-      <c r="I79" s="17" t="inlineStr"/>
+      <c r="H79" s="27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I79" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J79" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K79" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4111,9 +4948,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D80" s="17" t="n">
@@ -4126,9 +4963,20 @@
       <c r="G80" s="17" t="n">
         <v>86</v>
       </c>
-      <c r="H80" s="17" t="inlineStr"/>
-      <c r="I80" s="17" t="inlineStr"/>
+      <c r="H80" s="27" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="I80" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K80" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4145,9 +4993,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D81" s="17" t="n">
@@ -4160,9 +5008,20 @@
       <c r="G81" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="H81" s="17" t="inlineStr"/>
-      <c r="I81" s="17" t="inlineStr"/>
+      <c r="H81" s="27" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="I81" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J81" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K81" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4179,9 +5038,9 @@
           <t>Creative / media gen-AI</t>
         </is>
       </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D82" s="17" t="n">
@@ -4194,9 +5053,20 @@
       <c r="G82" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="H82" s="17" t="inlineStr"/>
-      <c r="I82" s="17" t="inlineStr"/>
+      <c r="H82" s="27" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="I82" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K82" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4213,9 +5083,9 @@
           <t>Creative / media gen-AI</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D83" s="17" t="n">
@@ -4228,9 +5098,20 @@
       <c r="G83" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="H83" s="17" t="inlineStr"/>
-      <c r="I83" s="17" t="inlineStr"/>
+      <c r="H83" s="27" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="I83" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J83" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K83" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4247,9 +5128,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D84" s="17" t="n">
@@ -4262,9 +5143,20 @@
       <c r="G84" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H84" s="17" t="inlineStr"/>
-      <c r="I84" s="17" t="inlineStr"/>
+      <c r="H84" s="30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I84" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4281,9 +5173,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D85" s="17" t="n">
@@ -4296,9 +5188,20 @@
       <c r="G85" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="H85" s="17" t="inlineStr"/>
-      <c r="I85" s="17" t="inlineStr"/>
+      <c r="H85" s="27" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I85" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4315,9 +5218,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D86" s="17" t="n">
@@ -4328,9 +5231,20 @@
         <v>4</v>
       </c>
       <c r="G86" s="17" t="n"/>
-      <c r="H86" s="17" t="inlineStr"/>
-      <c r="I86" s="17" t="inlineStr"/>
+      <c r="H86" s="27" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="I86" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K86" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4347,9 +5261,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D87" s="17" t="n">
@@ -4362,9 +5276,20 @@
       <c r="G87" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="H87" s="17" t="inlineStr"/>
-      <c r="I87" s="17" t="inlineStr"/>
+      <c r="H87" s="27" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="I87" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4381,9 +5306,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D88" s="17" t="n">
@@ -4396,9 +5321,20 @@
       <c r="G88" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="H88" s="17" t="inlineStr"/>
-      <c r="I88" s="17" t="inlineStr"/>
+      <c r="H88" s="27" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="I88" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K88" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4415,9 +5351,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D89" s="17" t="n">
@@ -4430,9 +5366,20 @@
       <c r="G89" s="17" t="n">
         <v>800</v>
       </c>
-      <c r="H89" s="17" t="inlineStr"/>
-      <c r="I89" s="17" t="inlineStr"/>
+      <c r="H89" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I89" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K89" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4449,9 +5396,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D90" s="17" t="n">
@@ -4464,9 +5411,20 @@
       <c r="G90" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="H90" s="17" t="inlineStr"/>
-      <c r="I90" s="17" t="inlineStr"/>
+      <c r="H90" s="27" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="I90" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -4483,9 +5441,9 @@
           <t>Customer-experience agents</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C91" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D91" s="17" t="n">
@@ -4498,9 +5456,20 @@
       <c r="G91" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="H91" s="17" t="inlineStr"/>
-      <c r="I91" s="17" t="inlineStr"/>
+      <c r="H91" s="27" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="I91" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J91" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K91" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4517,9 +5486,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C92" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D92" s="17" t="n">
@@ -4530,9 +5499,20 @@
         <v>0.47</v>
       </c>
       <c r="G92" s="17" t="n"/>
-      <c r="H92" s="17" t="inlineStr"/>
-      <c r="I92" s="17" t="inlineStr"/>
+      <c r="H92" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I92" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K92" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4549,9 +5529,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D93" s="17" t="n">
@@ -4562,9 +5542,20 @@
         <v>0.46</v>
       </c>
       <c r="G93" s="17" t="n"/>
-      <c r="H93" s="17" t="inlineStr"/>
-      <c r="I93" s="17" t="inlineStr"/>
+      <c r="H93" s="27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I93" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J93" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K93" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4581,9 +5572,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C94" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D94" s="17" t="n">
@@ -4596,9 +5587,20 @@
       <c r="G94" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H94" s="17" t="inlineStr"/>
-      <c r="I94" s="17" t="inlineStr"/>
+      <c r="H94" s="30" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="I94" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K94" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4615,9 +5617,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C95" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D95" s="17" t="n">
@@ -4628,9 +5630,20 @@
         <v>0.48</v>
       </c>
       <c r="G95" s="17" t="n"/>
-      <c r="H95" s="17" t="inlineStr"/>
-      <c r="I95" s="17" t="inlineStr"/>
+      <c r="H95" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I95" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J95" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K95" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4647,9 +5660,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C96" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D96" s="17" t="n">
@@ -4662,9 +5675,20 @@
       <c r="G96" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="H96" s="17" t="inlineStr"/>
-      <c r="I96" s="17" t="inlineStr"/>
+      <c r="H96" s="27" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I96" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J96" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K96" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4681,9 +5705,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C97" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D97" s="17" t="n">
@@ -4694,9 +5718,20 @@
         <v>0.15</v>
       </c>
       <c r="G97" s="17" t="n"/>
-      <c r="H97" s="17" t="inlineStr"/>
-      <c r="I97" s="17" t="inlineStr"/>
+      <c r="H97" s="27" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="I97" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J97" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K97" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4713,9 +5748,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C98" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D98" s="17" t="n">
@@ -4728,9 +5763,20 @@
       <c r="G98" s="17" t="n">
         <v>300</v>
       </c>
-      <c r="H98" s="17" t="inlineStr"/>
-      <c r="I98" s="17" t="inlineStr"/>
+      <c r="H98" s="27" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I98" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J98" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K98" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4747,9 +5793,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C99" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D99" s="17" t="n">
@@ -4762,9 +5808,20 @@
       <c r="G99" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="H99" s="17" t="inlineStr"/>
-      <c r="I99" s="17" t="inlineStr"/>
+      <c r="H99" s="27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I99" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J99" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K99" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4781,9 +5838,9 @@
           <t>Creative / media gen-AI</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C100" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D100" s="17" t="n">
@@ -4794,9 +5851,20 @@
         <v>0.97</v>
       </c>
       <c r="G100" s="17" t="n"/>
-      <c r="H100" s="17" t="inlineStr"/>
-      <c r="I100" s="17" t="inlineStr"/>
+      <c r="H100" s="27" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I100" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J100" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K100" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4813,9 +5881,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C101" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D101" s="17" t="n">
@@ -4826,9 +5894,20 @@
         <v>0.3</v>
       </c>
       <c r="G101" s="17" t="n"/>
-      <c r="H101" s="17" t="inlineStr"/>
-      <c r="I101" s="17" t="inlineStr"/>
+      <c r="H101" s="27" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I101" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J101" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K101" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4845,9 +5924,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C102" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D102" s="17" t="n">
@@ -4858,9 +5937,20 @@
         <v>0.1</v>
       </c>
       <c r="G102" s="17" t="n"/>
-      <c r="H102" s="17" t="inlineStr"/>
-      <c r="I102" s="17" t="inlineStr"/>
+      <c r="H102" s="27" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I102" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K102" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4877,9 +5967,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C103" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D103" s="17" t="n">
@@ -4892,9 +5982,20 @@
       <c r="G103" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="H103" s="17" t="inlineStr"/>
-      <c r="I103" s="17" t="inlineStr"/>
+      <c r="H103" s="27" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I103" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J103" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K103" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -4911,9 +6012,9 @@
           <t>Coding / dev tools</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C104" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D104" s="17" t="n">
@@ -4924,9 +6025,20 @@
         <v>1.02</v>
       </c>
       <c r="G104" s="17" t="n"/>
-      <c r="H104" s="17" t="inlineStr"/>
-      <c r="I104" s="17" t="inlineStr"/>
+      <c r="H104" s="27" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="I104" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J104" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K104" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4943,9 +6055,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C105" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D105" s="17" t="n">
@@ -4956,9 +6068,20 @@
         <v>1.01</v>
       </c>
       <c r="G105" s="17" t="n"/>
-      <c r="H105" s="17" t="inlineStr"/>
-      <c r="I105" s="17" t="inlineStr"/>
+      <c r="H105" s="27" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="I105" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J105" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K105" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -4975,9 +6098,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C106" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D106" s="17" t="n">
@@ -4990,9 +6113,20 @@
       <c r="G106" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="H106" s="17" t="inlineStr"/>
-      <c r="I106" s="17" t="inlineStr"/>
+      <c r="H106" s="27" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="I106" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J106" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K106" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5009,9 +6143,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
+      <c r="C107" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D107" s="17" t="n">
@@ -5022,9 +6156,20 @@
         <v>0.37</v>
       </c>
       <c r="G107" s="17" t="n"/>
-      <c r="H107" s="17" t="inlineStr"/>
-      <c r="I107" s="17" t="inlineStr"/>
+      <c r="H107" s="27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I107" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J107" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K107" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5041,9 +6186,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C108" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D108" s="17" t="n">
@@ -5054,9 +6199,20 @@
         <v>0.46</v>
       </c>
       <c r="G108" s="17" t="n"/>
-      <c r="H108" s="17" t="inlineStr"/>
-      <c r="I108" s="17" t="inlineStr"/>
+      <c r="H108" s="27" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I108" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J108" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K108" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5073,9 +6229,9 @@
           <t>Defense AI</t>
         </is>
       </c>
-      <c r="C109" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C109" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D109" s="17" t="n">
@@ -5086,9 +6242,20 @@
         <v>1.04</v>
       </c>
       <c r="G109" s="17" t="n"/>
-      <c r="H109" s="17" t="inlineStr"/>
-      <c r="I109" s="17" t="inlineStr"/>
+      <c r="H109" s="27" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="I109" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J109" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K109" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5105,9 +6272,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C110" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D110" s="17" t="n">
@@ -5118,9 +6285,20 @@
         <v>0.36</v>
       </c>
       <c r="G110" s="17" t="n"/>
-      <c r="H110" s="17" t="inlineStr"/>
-      <c r="I110" s="17" t="inlineStr"/>
+      <c r="H110" s="27" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I110" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J110" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K110" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5137,9 +6315,9 @@
           <t>Defense AI</t>
         </is>
       </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C111" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D111" s="17" t="n">
@@ -5150,9 +6328,20 @@
         <v>0.24</v>
       </c>
       <c r="G111" s="17" t="n"/>
-      <c r="H111" s="17" t="inlineStr"/>
-      <c r="I111" s="17" t="inlineStr"/>
+      <c r="H111" s="27" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I111" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J111" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K111" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5169,9 +6358,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C112" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D112" s="17" t="n">
@@ -5184,9 +6373,20 @@
       <c r="G112" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="H112" s="17" t="inlineStr"/>
-      <c r="I112" s="17" t="inlineStr"/>
+      <c r="H112" s="27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I112" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J112" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K112" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5203,9 +6403,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C113" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C113" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D113" s="17" t="n">
@@ -5216,9 +6416,20 @@
         <v>0.68</v>
       </c>
       <c r="G113" s="17" t="n"/>
-      <c r="H113" s="17" t="inlineStr"/>
-      <c r="I113" s="17" t="inlineStr"/>
+      <c r="H113" s="27" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="I113" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J113" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K113" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5235,9 +6446,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C114" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D114" s="17" t="n">
@@ -5250,9 +6461,20 @@
       <c r="G114" s="17" t="n">
         <v>752</v>
       </c>
-      <c r="H114" s="17" t="inlineStr"/>
-      <c r="I114" s="17" t="inlineStr"/>
+      <c r="H114" s="27" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="I114" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K114" s="17" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
@@ -5269,9 +6491,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C115" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D115" s="17" t="n">
@@ -5282,9 +6504,20 @@
         <v>0.51</v>
       </c>
       <c r="G115" s="17" t="n"/>
-      <c r="H115" s="17" t="inlineStr"/>
-      <c r="I115" s="17" t="inlineStr"/>
+      <c r="H115" s="27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I115" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J115" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K115" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5301,9 +6534,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C116" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C116" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D116" s="17" t="n">
@@ -5316,9 +6549,20 @@
       <c r="G116" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H116" s="17" t="inlineStr"/>
-      <c r="I116" s="17" t="inlineStr"/>
+      <c r="H116" s="27" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="I116" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J116" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5335,9 +6579,9 @@
           <t>Vertical AI — legal</t>
         </is>
       </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C117" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D117" s="17" t="n">
@@ -5350,9 +6594,20 @@
       <c r="G117" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="H117" s="17" t="inlineStr"/>
-      <c r="I117" s="17" t="inlineStr"/>
+      <c r="H117" s="27" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="I117" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J117" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K117" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5369,9 +6624,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C118" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D118" s="17" t="n">
@@ -5382,9 +6637,20 @@
         <v>0.3</v>
       </c>
       <c r="G118" s="17" t="n"/>
-      <c r="H118" s="17" t="inlineStr"/>
-      <c r="I118" s="17" t="inlineStr"/>
+      <c r="H118" s="27" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I118" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J118" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K118" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5401,9 +6667,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C119" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D119" s="17" t="n">
@@ -5414,9 +6680,20 @@
         <v>0.23</v>
       </c>
       <c r="G119" s="17" t="n"/>
-      <c r="H119" s="17" t="inlineStr"/>
-      <c r="I119" s="17" t="inlineStr"/>
+      <c r="H119" s="27" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I119" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J119" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K119" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5433,9 +6710,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C120" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D120" s="17" t="n">
@@ -5448,9 +6725,20 @@
       <c r="G120" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="H120" s="17" t="inlineStr"/>
-      <c r="I120" s="17" t="inlineStr"/>
+      <c r="H120" s="30" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I120" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J120" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K120" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5467,9 +6755,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C121" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D121" s="17" t="n">
@@ -5482,9 +6770,20 @@
       <c r="G121" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="H121" s="17" t="inlineStr"/>
-      <c r="I121" s="17" t="inlineStr"/>
+      <c r="H121" s="27" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I121" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J121" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K121" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5501,9 +6800,9 @@
           <t>Enterprise gen-AI</t>
         </is>
       </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C122" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D122" s="17" t="n">
@@ -5516,9 +6815,20 @@
       <c r="G122" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H122" s="17" t="inlineStr"/>
-      <c r="I122" s="17" t="inlineStr"/>
+      <c r="H122" s="27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I122" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J122" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K122" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5535,9 +6845,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C123" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D123" s="17" t="n">
@@ -5548,9 +6858,20 @@
         <v>0.2</v>
       </c>
       <c r="G123" s="17" t="n"/>
-      <c r="H123" s="17" t="inlineStr"/>
-      <c r="I123" s="17" t="inlineStr"/>
+      <c r="H123" s="27" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I123" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J123" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K123" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5567,9 +6888,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C124" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D124" s="17" t="n">
@@ -5580,9 +6901,20 @@
         <v>0.35</v>
       </c>
       <c r="G124" s="17" t="n"/>
-      <c r="H124" s="17" t="inlineStr"/>
-      <c r="I124" s="17" t="inlineStr"/>
+      <c r="H124" s="27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I124" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J124" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K124" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5599,9 +6931,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C125" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D125" s="17" t="n">
@@ -5612,9 +6944,20 @@
         <v>0.45</v>
       </c>
       <c r="G125" s="17" t="n"/>
-      <c r="H125" s="17" t="inlineStr"/>
-      <c r="I125" s="17" t="inlineStr"/>
+      <c r="H125" s="30" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I125" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J125" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K125" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5631,9 +6974,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C126" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D126" s="17" t="n">
@@ -5646,9 +6989,20 @@
       <c r="G126" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H126" s="17" t="inlineStr"/>
-      <c r="I126" s="17" t="inlineStr"/>
+      <c r="H126" s="27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I126" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J126" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K126" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5665,9 +7019,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C127" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D127" s="17" t="n">
@@ -5680,9 +7034,20 @@
       <c r="G127" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H127" s="17" t="inlineStr"/>
-      <c r="I127" s="17" t="inlineStr"/>
+      <c r="H127" s="27" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I127" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J127" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K127" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5699,9 +7064,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D128" s="17" t="n">
@@ -5714,9 +7079,20 @@
       <c r="G128" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H128" s="17" t="inlineStr"/>
-      <c r="I128" s="17" t="inlineStr"/>
+      <c r="H128" s="30" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I128" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J128" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K128" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5733,9 +7109,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C129" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D129" s="17" t="n">
@@ -5746,9 +7122,20 @@
         <v>0.29</v>
       </c>
       <c r="G129" s="17" t="n"/>
-      <c r="H129" s="17" t="inlineStr"/>
-      <c r="I129" s="17" t="inlineStr"/>
+      <c r="H129" s="27" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I129" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J129" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K129" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5765,9 +7152,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D130" s="17" t="n">
@@ -5780,9 +7167,20 @@
       <c r="G130" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="H130" s="17" t="inlineStr"/>
-      <c r="I130" s="17" t="inlineStr"/>
+      <c r="H130" s="27" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I130" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5799,9 +7197,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C131" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D131" s="17" t="n">
@@ -5812,9 +7210,20 @@
         <v>0.28</v>
       </c>
       <c r="G131" s="17" t="n"/>
-      <c r="H131" s="17" t="inlineStr"/>
-      <c r="I131" s="17" t="inlineStr"/>
+      <c r="H131" s="27" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="I131" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J131" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K131" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5831,9 +7240,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C132" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D132" s="17" t="n">
@@ -5846,9 +7255,20 @@
       <c r="G132" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H132" s="17" t="inlineStr"/>
-      <c r="I132" s="17" t="inlineStr"/>
+      <c r="H132" s="27" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I132" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5865,9 +7285,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C133" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D133" s="17" t="n">
@@ -5878,9 +7298,20 @@
         <v>0.55</v>
       </c>
       <c r="G133" s="17" t="n"/>
-      <c r="H133" s="17" t="inlineStr"/>
-      <c r="I133" s="17" t="inlineStr"/>
+      <c r="H133" s="30" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I133" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J133" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K133" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5897,9 +7328,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C134" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D134" s="17" t="n">
@@ -5910,9 +7341,20 @@
         <v>0.52</v>
       </c>
       <c r="G134" s="17" t="n"/>
-      <c r="H134" s="17" t="inlineStr"/>
-      <c r="I134" s="17" t="inlineStr"/>
+      <c r="H134" s="27" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I134" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J134" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K134" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5929,9 +7371,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C135" s="29" t="inlineStr">
+        <is>
+          <t>AI-BIO</t>
         </is>
       </c>
       <c r="D135" s="17" t="n">
@@ -5942,9 +7384,20 @@
         <v>0.47</v>
       </c>
       <c r="G135" s="17" t="n"/>
-      <c r="H135" s="17" t="inlineStr"/>
-      <c r="I135" s="17" t="inlineStr"/>
+      <c r="H135" s="30" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I135" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J135" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K135" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -5961,9 +7414,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C136" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D136" s="17" t="n">
@@ -5976,9 +7429,20 @@
       <c r="G136" s="17" t="n">
         <v>350</v>
       </c>
-      <c r="H136" s="17" t="inlineStr"/>
-      <c r="I136" s="17" t="inlineStr"/>
+      <c r="H136" s="27" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="I136" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J136" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K136" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -5995,9 +7459,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C137" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C137" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D137" s="17" t="n">
@@ -6010,9 +7474,20 @@
       <c r="G137" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="H137" s="17" t="inlineStr"/>
-      <c r="I137" s="17" t="inlineStr"/>
+      <c r="H137" s="30" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="I137" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J137" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K137" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6029,9 +7504,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C138" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C138" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D138" s="17" t="n">
@@ -6042,9 +7517,20 @@
         <v>0.35</v>
       </c>
       <c r="G138" s="17" t="n"/>
-      <c r="H138" s="17" t="inlineStr"/>
-      <c r="I138" s="17" t="inlineStr"/>
+      <c r="H138" s="30" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I138" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J138" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6061,9 +7547,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C139" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C139" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D139" s="17" t="n">
@@ -6074,9 +7560,20 @@
         <v>0.33</v>
       </c>
       <c r="G139" s="17" t="n"/>
-      <c r="H139" s="17" t="inlineStr"/>
-      <c r="I139" s="17" t="inlineStr"/>
+      <c r="H139" s="27" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="I139" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J139" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K139" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6093,9 +7590,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C140" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D140" s="17" t="n">
@@ -6108,9 +7605,20 @@
       <c r="G140" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H140" s="17" t="inlineStr"/>
-      <c r="I140" s="17" t="inlineStr"/>
+      <c r="H140" s="27" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I140" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J140" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6127,9 +7635,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C141" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D141" s="17" t="n">
@@ -6142,9 +7650,20 @@
       <c r="G141" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H141" s="17" t="inlineStr"/>
-      <c r="I141" s="17" t="inlineStr"/>
+      <c r="H141" s="27" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="I141" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J141" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K141" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6161,9 +7680,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C142" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C142" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D142" s="17" t="n">
@@ -6174,9 +7693,20 @@
         <v>0.18</v>
       </c>
       <c r="G142" s="17" t="n"/>
-      <c r="H142" s="17" t="inlineStr"/>
-      <c r="I142" s="17" t="inlineStr"/>
+      <c r="H142" s="27" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I142" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J142" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K142" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6193,9 +7723,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C143" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D143" s="17" t="n">
@@ -6208,9 +7738,20 @@
       <c r="G143" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="H143" s="17" t="inlineStr"/>
-      <c r="I143" s="17" t="inlineStr"/>
+      <c r="H143" s="27" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I143" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J143" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K143" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6227,9 +7768,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C144" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D144" s="17" t="n">
@@ -6242,9 +7783,20 @@
       <c r="G144" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="H144" s="17" t="inlineStr"/>
-      <c r="I144" s="17" t="inlineStr"/>
+      <c r="H144" s="27" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I144" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J144" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K144" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6261,9 +7813,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C145" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C145" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D145" s="17" t="n">
@@ -6276,9 +7828,20 @@
       <c r="G145" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="H145" s="17" t="inlineStr"/>
-      <c r="I145" s="17" t="inlineStr"/>
+      <c r="H145" s="27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I145" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J145" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K145" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6295,9 +7858,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C146" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D146" s="17" t="n">
@@ -6308,9 +7871,20 @@
         <v>0.21</v>
       </c>
       <c r="G146" s="17" t="n"/>
-      <c r="H146" s="17" t="inlineStr"/>
-      <c r="I146" s="17" t="inlineStr"/>
+      <c r="H146" s="27" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="I146" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J146" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K146" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6327,9 +7901,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C147" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D147" s="17" t="n">
@@ -6342,9 +7916,20 @@
       <c r="G147" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="H147" s="17" t="inlineStr"/>
-      <c r="I147" s="17" t="inlineStr"/>
+      <c r="H147" s="27" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="I147" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J147" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K147" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6361,9 +7946,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C148" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D148" s="17" t="n">
@@ -6374,9 +7959,20 @@
         <v>0.27</v>
       </c>
       <c r="G148" s="17" t="n"/>
-      <c r="H148" s="17" t="inlineStr"/>
-      <c r="I148" s="17" t="inlineStr"/>
+      <c r="H148" s="27" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="I148" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J148" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K148" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6393,9 +7989,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C149" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C149" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D149" s="17" t="n">
@@ -6408,9 +8004,20 @@
       <c r="G149" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="H149" s="17" t="inlineStr"/>
-      <c r="I149" s="17" t="inlineStr"/>
+      <c r="H149" s="27" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I149" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J149" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K149" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6427,9 +8034,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C150" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D150" s="17" t="n">
@@ -6440,9 +8047,20 @@
         <v>0.27</v>
       </c>
       <c r="G150" s="17" t="n"/>
-      <c r="H150" s="17" t="inlineStr"/>
-      <c r="I150" s="17" t="inlineStr"/>
+      <c r="H150" s="30" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I150" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J150" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K150" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6459,9 +8077,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C151" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D151" s="17" t="n">
@@ -6472,9 +8090,20 @@
         <v>0.18</v>
       </c>
       <c r="G151" s="17" t="n"/>
-      <c r="H151" s="17" t="inlineStr"/>
-      <c r="I151" s="17" t="inlineStr"/>
+      <c r="H151" s="27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I151" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J151" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K151" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6491,9 +8120,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C152" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D152" s="17" t="n">
@@ -6506,9 +8135,20 @@
       <c r="G152" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H152" s="17" t="inlineStr"/>
-      <c r="I152" s="17" t="inlineStr"/>
+      <c r="H152" s="30" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I152" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J152" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K152" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6525,9 +8165,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C153" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D153" s="17" t="n">
@@ -6540,9 +8180,20 @@
       <c r="G153" s="17" t="n">
         <v>154</v>
       </c>
-      <c r="H153" s="17" t="inlineStr"/>
-      <c r="I153" s="17" t="inlineStr"/>
+      <c r="H153" s="27" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="I153" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J153" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K153" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6559,9 +8210,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C154" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D154" s="17" t="n">
@@ -6574,9 +8225,20 @@
       <c r="G154" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="H154" s="17" t="inlineStr"/>
-      <c r="I154" s="17" t="inlineStr"/>
+      <c r="H154" s="30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I154" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J154" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K154" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6593,9 +8255,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C155" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D155" s="17" t="n">
@@ -6606,9 +8268,20 @@
         <v>0.27</v>
       </c>
       <c r="G155" s="17" t="n"/>
-      <c r="H155" s="17" t="inlineStr"/>
-      <c r="I155" s="17" t="inlineStr"/>
+      <c r="H155" s="27" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="I155" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J155" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K155" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6625,9 +8298,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C156" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C156" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D156" s="17" t="n">
@@ -6638,9 +8311,20 @@
         <v>0.2</v>
       </c>
       <c r="G156" s="17" t="n"/>
-      <c r="H156" s="17" t="inlineStr"/>
-      <c r="I156" s="17" t="inlineStr"/>
+      <c r="H156" s="27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I156" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J156" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K156" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6657,9 +8341,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C157" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C157" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D157" s="17" t="n">
@@ -6672,9 +8356,20 @@
       <c r="G157" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="H157" s="17" t="inlineStr"/>
-      <c r="I157" s="17" t="inlineStr"/>
+      <c r="H157" s="30" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="I157" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J157" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K157" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6691,9 +8386,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C158" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C158" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D158" s="17" t="n">
@@ -6704,9 +8399,20 @@
         <v>0.27</v>
       </c>
       <c r="G158" s="17" t="n"/>
-      <c r="H158" s="17" t="inlineStr"/>
-      <c r="I158" s="17" t="inlineStr"/>
+      <c r="H158" s="30" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I158" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J158" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K158" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6723,9 +8429,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C159" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D159" s="17" t="n">
@@ -6738,9 +8444,20 @@
       <c r="G159" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="H159" s="17" t="inlineStr"/>
-      <c r="I159" s="17" t="inlineStr"/>
+      <c r="H159" s="27" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="I159" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J159" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K159" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6757,9 +8474,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C160" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C160" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D160" s="17" t="n">
@@ -6772,9 +8489,20 @@
       <c r="G160" s="17" t="n">
         <v>191</v>
       </c>
-      <c r="H160" s="17" t="inlineStr"/>
-      <c r="I160" s="17" t="inlineStr"/>
+      <c r="H160" s="27" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="I160" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J160" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K160" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6791,9 +8519,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
+      <c r="C161" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D161" s="17" t="n">
@@ -6806,9 +8534,20 @@
       <c r="G161" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="H161" s="17" t="inlineStr"/>
-      <c r="I161" s="17" t="inlineStr"/>
+      <c r="H161" s="27" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I161" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J161" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K161" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -6825,9 +8564,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C162" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D162" s="17" t="n">
@@ -6838,9 +8577,20 @@
         <v>0.21</v>
       </c>
       <c r="G162" s="17" t="n"/>
-      <c r="H162" s="17" t="inlineStr"/>
-      <c r="I162" s="17" t="inlineStr"/>
+      <c r="H162" s="30" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I162" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J162" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K162" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6857,9 +8607,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C163" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C163" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D163" s="17" t="n">
@@ -6870,9 +8620,20 @@
         <v>0.19</v>
       </c>
       <c r="G163" s="17" t="n"/>
-      <c r="H163" s="17" t="inlineStr"/>
-      <c r="I163" s="17" t="inlineStr"/>
+      <c r="H163" s="30" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I163" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J163" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K163" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6889,9 +8650,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C164" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D164" s="17" t="n">
@@ -6902,9 +8663,20 @@
         <v>0.16</v>
       </c>
       <c r="G164" s="17" t="n"/>
-      <c r="H164" s="17" t="inlineStr"/>
-      <c r="I164" s="17" t="inlineStr"/>
+      <c r="H164" s="30" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="I164" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J164" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K164" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6921,9 +8693,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>Consumer Products and Services (B2C)</t>
+      <c r="C165" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D165" s="17" t="n">
@@ -6936,9 +8708,20 @@
       <c r="G165" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="H165" s="17" t="inlineStr"/>
-      <c r="I165" s="17" t="inlineStr"/>
+      <c r="H165" s="27" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I165" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J165" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K165" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6955,9 +8738,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C166" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D166" s="17" t="n">
@@ -6970,9 +8753,20 @@
       <c r="G166" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="H166" s="17" t="inlineStr"/>
-      <c r="I166" s="17" t="inlineStr"/>
+      <c r="H166" s="30" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I166" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J166" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K166" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -6989,9 +8783,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C167" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D167" s="17" t="n">
@@ -7004,9 +8798,20 @@
       <c r="G167" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H167" s="17" t="inlineStr"/>
-      <c r="I167" s="17" t="inlineStr"/>
+      <c r="H167" s="30" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="I167" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J167" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K167" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7023,9 +8828,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>Business Products and Services (B2B)</t>
+      <c r="C168" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D168" s="17" t="n">
@@ -7036,9 +8841,20 @@
         <v>0.34</v>
       </c>
       <c r="G168" s="17" t="n"/>
-      <c r="H168" s="17" t="inlineStr"/>
-      <c r="I168" s="17" t="inlineStr"/>
+      <c r="H168" s="27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I168" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J168" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K168" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7055,9 +8871,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C169" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D169" s="17" t="n">
@@ -7070,9 +8886,20 @@
       <c r="G169" s="17" t="n">
         <v>140</v>
       </c>
-      <c r="H169" s="17" t="inlineStr"/>
-      <c r="I169" s="17" t="inlineStr"/>
+      <c r="H169" s="27" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="I169" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J169" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K169" s="17" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
@@ -7089,9 +8916,9 @@
           <t>Physical AI / robotics / autonomy</t>
         </is>
       </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C170" s="29" t="inlineStr">
+        <is>
+          <t>AI-AUTO</t>
         </is>
       </c>
       <c r="D170" s="17" t="n">
@@ -7104,9 +8931,20 @@
       <c r="G170" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H170" s="17" t="inlineStr"/>
-      <c r="I170" s="17" t="inlineStr"/>
+      <c r="H170" s="30" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="I170" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J170" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K170" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7123,9 +8961,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C171" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C171" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D171" s="17" t="n">
@@ -7136,9 +8974,20 @@
         <v>0.18</v>
       </c>
       <c r="G171" s="17" t="n"/>
-      <c r="H171" s="17" t="inlineStr"/>
-      <c r="I171" s="17" t="inlineStr"/>
+      <c r="H171" s="27" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I171" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J171" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K171" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7155,9 +9004,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C172" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D172" s="17" t="n">
@@ -7168,9 +9017,20 @@
         <v>0.16</v>
       </c>
       <c r="G172" s="17" t="n"/>
-      <c r="H172" s="17" t="inlineStr"/>
-      <c r="I172" s="17" t="inlineStr"/>
+      <c r="H172" s="30" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I172" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J172" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K172" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7187,9 +9047,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C173" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D173" s="17" t="n">
@@ -7200,9 +9060,20 @@
         <v>0.13</v>
       </c>
       <c r="G173" s="17" t="n"/>
-      <c r="H173" s="17" t="inlineStr"/>
-      <c r="I173" s="17" t="inlineStr"/>
+      <c r="H173" s="27" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="I173" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J173" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K173" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7219,9 +9090,9 @@
           <t>Vertical AI — healthcare</t>
         </is>
       </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="C174" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D174" s="17" t="n">
@@ -7232,9 +9103,20 @@
         <v>0.12</v>
       </c>
       <c r="G174" s="17" t="n"/>
-      <c r="H174" s="17" t="inlineStr"/>
-      <c r="I174" s="17" t="inlineStr"/>
+      <c r="H174" s="30" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I174" s="31" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
       <c r="J174" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K174" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7251,9 +9133,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C175" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C175" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D175" s="17" t="n">
@@ -7264,9 +9146,20 @@
         <v>0.05</v>
       </c>
       <c r="G175" s="17" t="n"/>
-      <c r="H175" s="17" t="inlineStr"/>
-      <c r="I175" s="17" t="inlineStr"/>
+      <c r="H175" s="27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I175" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J175" s="17" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K175" s="17" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
@@ -7283,9 +9176,9 @@
           <t>AI application (horizontal/vertical)</t>
         </is>
       </c>
-      <c r="C176" s="16" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
+      <c r="C176" s="29" t="inlineStr">
+        <is>
+          <t>AI-APP</t>
         </is>
       </c>
       <c r="D176" s="17" t="n">
@@ -7296,28 +9189,40 @@
         <v>0.05</v>
       </c>
       <c r="G176" s="17" t="n"/>
-      <c r="H176" s="17" t="inlineStr"/>
-      <c r="I176" s="17" t="inlineStr"/>
+      <c r="H176" s="27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="I176" s="28" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="J176" s="17" t="inlineStr">
         <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="K176" s="17" t="inlineStr">
+        <is>
           <t>S2</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="24" t="inlineStr">
-        <is>
-          <t>Gold AIBQ code = one of the 20 deep-researched names (composite shown). Morningstar Model $B = the index mark-to-model value (Unicorn 20 only); blank elsewhere. Valuations are PitchBook round marks and may differ from the Morningstar model (see Comparison tab).</t>
-        </is>
-      </c>
-    </row>
+    <row r="178" ht="46" customHeight="1">
+      <c r="A178" s="35" t="inlineStr">
+        <is>
+          <t>AIBQ code assigned to EVERY name from its stack layer (Model-&gt;AI-INFRA · silicon-&gt;AI-ACCEL · GPU-cloud-&gt;AI-INFRA · data/MLOps-&gt;AI-PLAT · robotics/autonomy-&gt;AI-AUTO · bio-&gt;AI-BIO · else AI-APP). Composite shown for ALL: 'Deep' = hand-researched (gold, verified code/composite; PBQ-routed names keep their PBQ code); 'Screen' = automated data-driven composite (relative, wide band — see Overview). Revenue = PitchBook where disclosed (blank = undisclosed). Morningstar Model $B = Unicorn-20 mark-to-model only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A178:J178"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A178:K179"/>
+    <mergeCell ref="A24:K24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7439,7 +9344,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Mine is US-only (938); the trackers are global (1,556-1,743). US is roughly half the global count — the frames are consistent once scope is aligned.</t>
         </is>
@@ -7563,7 +9468,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>The gap is definitional: my AIBQ is a strict 4-question routing (model-centric); Monitor tags any company with the AI/ML vertical (broader). All three converge on the key point: AI is a minority of companies but ~half of unicorn value.</t>
         </is>
@@ -8324,7 +10229,7 @@
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B47" s="36" t="inlineStr">
         <is>
           <t>Where I diverge: I over-adopted rumored/announced marks on Revolut ($200B vs $94B model), Cursor ($60B acq vs $33B), Ripple ($40B vs $20B), Kraken ($20B vs $12B), Epic ($22.5B vs $14B, a 'decline' name). Morningstar marks ABOVE my round on the AI leaders — Anthropic ($1.27T), Neuralink ($52B), Anduril, Applied Intuition. Recommend adopting the model mark (or showing all three) for the next cut.</t>
         </is>
